--- a/data/cultures.xlsx
+++ b/data/cultures.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="_Tree Index" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Serrovane" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Kestrel Reach" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Tree Index" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Serrovane" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kestrel Reach" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,21 +610,21 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Raised in Serrovane</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>You know Serrovine and Common.
-You gain a +1 status bonus to Diplomacy checks toward those who share the same Culture. When you are Expert in your Origin Constellation, the bonus increases to +2. Master: +3. Legendary: +4.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+You gain a +1 Condition bonus to Diplomacy checks toward those who share the same Culture. When you are Expert in your Origin Constellation, the bonus increases to +2. Master: +3. Legendary: +4.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -637,21 +637,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Serrovanian</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Name one creature that has broken a bargain, a truce, or a formal challenge with you. You gain a +1 circumstance bonus to Attack rolls and Defense rolls against that creature until the encounter ends. You may have only one Oathbound creature at a time.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+          <t>Name one creature that has broken a bargain, a truce, or a formal challenge with you. You gain a +1 Situation bonus to Attack rolls and Defense rolls against that creature until the encounter ends. You may have only one Oathbound creature at a time.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -664,13 +664,13 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Serrovanian</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Read legal, and infernal, contracts at a glance.</t>
@@ -678,11 +678,11 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>+2 circumstance to notice hidden clauses, traps, and altered terms in any agreement.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+          <t>+2 Situation to notice hidden clauses, traps, and altered terms in any agreement.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -695,13 +695,13 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Serrovanian</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Court manners are armor.</t>
@@ -709,11 +709,11 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>+1 circumstance to checks against Intimidation and social manipulation.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t>+1 Situation to checks against Intimidation and social manipulation.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -803,26 +803,26 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Raised in the Kestrel Reach</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>You know Reachspeak and Common.
-You gain a +1 status bonus to Diplomacy checks toward those who share the same Culture. When you are Expert in your Origin Constellation, the bonus increases to +2. Master: +3. Legendary: +4.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+You gain a +1 Condition bonus to Diplomacy checks toward those who share the same Culture. When you are Expert in your Origin Constellation, the bonus increases to +2. Master: +3. Legendary: +4.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Quick Tongue ◇</t>
+          <t>Quick Tongue ⓿</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -830,25 +830,60 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Reacher</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>You gain the Quick Tongue action:
-Quick Tongue ◇
-Trigger You critically fail a Diplomacy check.
-Requirements You're in a settlement or community, and you haven't used Quick Tongue in this settlement or community within the past month.
+          <r>
+            <t xml:space="preserve">You gain the Quick Tongue action:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Quick Tongue ⓿</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Trigger</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> You critically fail a Diplomacy check.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Requirements</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> You're in a settlement or community, and you haven't used Quick Tongue in this settlement or community within the past month.
 Reroll the triggering Diplomacy check, using the second result.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+          </r>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -861,21 +896,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Reacher</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>You ignore difficult terrain from mud, decking, loose stone, and shallow water, and your first Stride each encounter is 5 feet longer.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+          <t>You ignore difficult terrain from mud, decking, loose stone, and shallow water, and your first Move each encounter is 1 foot longer.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -888,21 +923,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Reacher</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>You always know an item's fair price, and gain +2 circumstance to Diplomacy and Guile checks when trading.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t>You always know an item's fair price, and gain +2 Situation to Diplomacy and Guile checks when trading.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/cultures.xlsx
+++ b/data/cultures.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="5415" yWindow="5415" windowWidth="36450" windowHeight="13980" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Tree Index" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,14 +11,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kestrel Reach" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,9 +27,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -42,7 +47,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E5F6B"/>
+        <fgColor rgb="FF0E5F6B"/>
       </patternFill>
     </fill>
   </fills>
@@ -68,7 +73,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -468,7 +473,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="45" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Serrovane</t>
@@ -495,7 +500,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Kestrel Reach</t>
@@ -533,14 +538,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -593,8 +596,13 @@
           <t>Grants (restricted TPs this talent gives)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Serrovanian</t>
@@ -625,8 +633,13 @@
       </c>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
-    </row>
-    <row r="3">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Oathbound</t>
@@ -653,7 +666,7 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Contract Literate</t>
@@ -726,14 +739,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -786,8 +797,13 @@
           <t>Grants (restricted TPs this talent gives)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Reacher</t>
@@ -819,7 +835,7 @@
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
     </row>
-    <row r="3">
+    <row r="3" ht="75" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Quick Tongue ⓿</t>
@@ -846,23 +862,10 @@
           </r>
           <r>
             <rPr>
-              <rFont val="Calibri"/>
               <b val="1"/>
-              <sz val="11"/>
             </rPr>
-            <t>Quick Tongue ⓿</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Trigger</t>
+            <t>Quick Tongue ⓿
+Trigger</t>
           </r>
           <r>
             <t xml:space="preserve"> You critically fail a Diplomacy check.
@@ -870,9 +873,7 @@
           </r>
           <r>
             <rPr>
-              <rFont val="Calibri"/>
               <b val="1"/>
-              <sz val="11"/>
             </rPr>
             <t>Requirements</t>
           </r>
@@ -885,7 +886,7 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Riverfoot</t>

--- a/data/cultures.xlsx
+++ b/data/cultures.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -548,6 +548,8 @@
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -599,6 +601,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Enabled?</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
         </is>
       </c>
     </row>
@@ -739,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -749,6 +756,8 @@
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -800,6 +809,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Enabled?</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
         </is>
       </c>
     </row>
